--- a/data_result/2026-05-06/gwnet.xlsx
+++ b/data_result/2026-05-06/gwnet.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -766,65 +766,132 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>pems07</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>84.0351±65.6751</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>38.5628±0.3531</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>54.11%</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>106.4075±71.1432</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>57.5130±0.3553</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>45.95%</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23.9578±0.0384</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>24.4769±0.0492</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-2.17%</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>37.1343±0.0243</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>37.6414±0.0154</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>-1.37%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>pems08</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>24.5838±0.1305</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>58.1463±43.0540</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>-136.52%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>38.2122±0.3065</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>76.6969±49.1842</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>-100.71%</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>16.4110±0.0940</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>17.2000±0.3686</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>-4.81%</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>25.3192±0.0967</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>26.0835±0.3174</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>-3.02%</t>
         </is>
